--- a/outputs/shap_rank_compare.xlsx
+++ b/outputs/shap_rank_compare.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.002809020851627793</v>
+        <v>0.002985350077146904</v>
       </c>
     </row>
     <row r="3">
@@ -471,11 +471,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.001277305007365612</v>
+        <v>0.001895417864811435</v>
       </c>
     </row>
     <row r="4">
@@ -491,11 +491,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Particle content</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.001069959124118895</v>
+        <v>0.00163546158123836</v>
       </c>
     </row>
     <row r="5">
@@ -511,11 +511,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.001020275653224587</v>
+        <v>0.001593826710928852</v>
       </c>
     </row>
     <row r="6">
@@ -531,11 +531,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>Particle content</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.0008804007069923614</v>
+        <v>0.001518609059984328</v>
       </c>
     </row>
     <row r="7">
@@ -551,11 +551,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>clay content</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0005688354263480732</v>
+        <v>0.001352892925951892</v>
       </c>
     </row>
     <row r="8">
@@ -571,11 +571,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.0005501845004960159</v>
+        <v>0.001343562242622056</v>
       </c>
     </row>
     <row r="9">
@@ -591,11 +591,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>water content</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0005470213827368297</v>
+        <v>0.001298728128061271</v>
       </c>
     </row>
     <row r="10">
@@ -611,11 +611,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bulk density</t>
+          <t>clay content</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.0004997335651026446</v>
+        <v>0.0009926296738822771</v>
       </c>
     </row>
     <row r="11">
@@ -631,11 +631,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.0004330773297888868</v>
+        <v>0.0009301586022462516</v>
       </c>
     </row>
     <row r="12">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.006806367805298506</v>
+        <v>0.008442509671309393</v>
       </c>
     </row>
     <row r="13">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.004022583352756902</v>
+        <v>0.0053632803351059</v>
       </c>
     </row>
     <row r="14">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.002143335324637184</v>
+        <v>0.002072383727660449</v>
       </c>
     </row>
     <row r="15">
@@ -711,11 +711,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.001637444540519002</v>
+        <v>0.002069257706163208</v>
       </c>
     </row>
     <row r="16">
@@ -731,11 +731,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>clay content</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.001442604126465343</v>
+        <v>0.001658777789270421</v>
       </c>
     </row>
     <row r="17">
@@ -751,11 +751,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>Vegetation cover type</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.001368485849056828</v>
+        <v>0.001486720971068863</v>
       </c>
     </row>
     <row r="18">
@@ -771,11 +771,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.001229082147524299</v>
+        <v>0.001396008814806924</v>
       </c>
     </row>
     <row r="19">
@@ -791,11 +791,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>bulk density</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.00121519481411261</v>
+        <v>0.001353391208800569</v>
       </c>
     </row>
     <row r="20">
@@ -811,11 +811,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sand content</t>
+          <t>water content</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.001106144385715793</v>
+        <v>0.001306386295864918</v>
       </c>
     </row>
     <row r="21">
@@ -831,11 +831,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bulk density</t>
+          <t>sand content</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.001066726993743931</v>
+        <v>0.001247905168373032</v>
       </c>
     </row>
     <row r="22">
@@ -851,11 +851,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Distance from pollution source</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.001323768027241203</v>
+        <v>0.001422442923228084</v>
       </c>
     </row>
     <row r="23">
@@ -871,11 +871,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Distance from pollution source</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.001104395006638715</v>
+        <v>0.001363546420732245</v>
       </c>
     </row>
     <row r="24">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.0006022961360067816</v>
+        <v>0.0008853263062860931</v>
       </c>
     </row>
     <row r="25">
@@ -911,11 +911,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.0005097307091135654</v>
+        <v>0.0008764458329094064</v>
       </c>
     </row>
     <row r="26">
@@ -931,11 +931,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>clay content</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.0004266786814112644</v>
+        <v>0.0008251862342868509</v>
       </c>
     </row>
     <row r="27">
@@ -951,11 +951,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>bulk density</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.0003802874268661887</v>
+        <v>0.0006355543323763054</v>
       </c>
     </row>
     <row r="28">
@@ -971,11 +971,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.0003762538977960967</v>
+        <v>0.0006265045699482417</v>
       </c>
     </row>
     <row r="29">
@@ -991,11 +991,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.0003675674866646925</v>
+        <v>0.0006153696826327451</v>
       </c>
     </row>
     <row r="30">
@@ -1011,11 +1011,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>sand content</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.000363066515260627</v>
+        <v>0.0005921878909063309</v>
       </c>
     </row>
     <row r="31">
@@ -1031,11 +1031,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sand content</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.0003559361399366182</v>
+        <v>0.0005850770210008313</v>
       </c>
     </row>
     <row r="32">
@@ -1051,11 +1051,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Distance from pollution source</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.002084537646683202</v>
+        <v>0.002570680637866047</v>
       </c>
     </row>
     <row r="33">
@@ -1071,11 +1071,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Distance from pollution source</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.00191324062662261</v>
+        <v>0.002482781878158846</v>
       </c>
     </row>
     <row r="34">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.001166674034202515</v>
+        <v>0.001773142388002498</v>
       </c>
     </row>
     <row r="35">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.0009688396380503405</v>
+        <v>0.001672626322820747</v>
       </c>
     </row>
     <row r="36">
@@ -1131,11 +1131,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sand content</t>
+          <t>Particle content</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.000925749777084377</v>
+        <v>0.001619668755754447</v>
       </c>
     </row>
     <row r="37">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>soil type</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.0008205652719925638</v>
+        <v>0.001570283741417597</v>
       </c>
     </row>
     <row r="38">
@@ -1171,11 +1171,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>sand content</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.0007279860806308847</v>
+        <v>0.001490883894564874</v>
       </c>
     </row>
     <row r="39">
@@ -1191,11 +1191,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.0007058686134658387</v>
+        <v>0.001416304155015524</v>
       </c>
     </row>
     <row r="40">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.0005138600435878971</v>
+        <v>0.001366394763293215</v>
       </c>
     </row>
     <row r="41">
@@ -1231,11 +1231,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>bulk density</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.000496527754720546</v>
+        <v>0.001365630607525929</v>
       </c>
     </row>
     <row r="42">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.007516256044716408</v>
+        <v>0.008148636287739276</v>
       </c>
     </row>
     <row r="43">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.004682415671441221</v>
+        <v>0.004619357069258469</v>
       </c>
     </row>
     <row r="44">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.002536040797761452</v>
+        <v>0.003170523645533209</v>
       </c>
     </row>
     <row r="45">
@@ -1311,11 +1311,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.001930319015692491</v>
+        <v>0.002615323747435834</v>
       </c>
     </row>
     <row r="46">
@@ -1331,11 +1331,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sand content</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.001612504316795036</v>
+        <v>0.002565466241682067</v>
       </c>
     </row>
     <row r="47">
@@ -1351,11 +1351,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>sand content</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.001223404855327183</v>
+        <v>0.002092652056340221</v>
       </c>
     </row>
     <row r="48">
@@ -1371,11 +1371,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vegetation cover type</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.001194079740521346</v>
+        <v>0.002053936337194521</v>
       </c>
     </row>
     <row r="49">
@@ -1391,11 +1391,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>clay content</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.001168363225466081</v>
+        <v>0.001568497467498666</v>
       </c>
     </row>
     <row r="50">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.001002036358169839</v>
+        <v>0.001519174851465614</v>
       </c>
     </row>
     <row r="51">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.0007527125773187619</v>
+        <v>0.001368722017900121</v>
       </c>
     </row>
     <row r="52">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.01272076712909736</v>
+        <v>0.01673277497997837</v>
       </c>
     </row>
     <row r="53">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.003176723332559266</v>
+        <v>0.007356563851002161</v>
       </c>
     </row>
     <row r="54">
@@ -1491,11 +1491,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.002927833146578329</v>
+        <v>0.00578472159485509</v>
       </c>
     </row>
     <row r="55">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.002584950625478627</v>
+        <v>0.003695715855752893</v>
       </c>
     </row>
     <row r="56">
@@ -1531,11 +1531,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Particle content</t>
+          <t>bulk density</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.002503678654963128</v>
+        <v>0.002613491878010151</v>
       </c>
     </row>
     <row r="57">
@@ -1551,11 +1551,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.002434889047399698</v>
+        <v>0.002608478485367729</v>
       </c>
     </row>
     <row r="58">
@@ -1571,11 +1571,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.002389832815127436</v>
+        <v>0.001865640612876551</v>
       </c>
     </row>
     <row r="59">
@@ -1591,11 +1591,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>bulk density</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.002011714662663814</v>
+        <v>0.001801180611410288</v>
       </c>
     </row>
     <row r="60">
@@ -1611,11 +1611,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>sand content</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.001927363600089923</v>
+        <v>0.0008445157547234119</v>
       </c>
     </row>
     <row r="61">
@@ -1631,11 +1631,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>clay content</t>
+          <t>soil type</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.001821122158680106</v>
+        <v>0.0008385338230732261</v>
       </c>
     </row>
     <row r="62">
@@ -1651,11 +1651,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>clay content</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.002627062756985226</v>
+        <v>0.002485803789015704</v>
       </c>
     </row>
     <row r="63">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.002380231097987822</v>
+        <v>0.002389821749395334</v>
       </c>
     </row>
     <row r="64">
@@ -1691,11 +1691,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>Particle content</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.001945722246091464</v>
+        <v>0.002360550699280148</v>
       </c>
     </row>
     <row r="65">
@@ -1711,11 +1711,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.001683950315826315</v>
+        <v>0.002251560983886866</v>
       </c>
     </row>
     <row r="66">
@@ -1731,11 +1731,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>clay content</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.00127050533885981</v>
+        <v>0.002243968037344277</v>
       </c>
     </row>
     <row r="67">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.001264002404103031</v>
+        <v>0.002239872375472674</v>
       </c>
     </row>
     <row r="68">
@@ -1771,11 +1771,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>water content</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.001059222666523815</v>
+        <v>0.001974183636384278</v>
       </c>
     </row>
     <row r="69">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.001011710945416366</v>
+        <v>0.001688511038669794</v>
       </c>
     </row>
     <row r="70">
@@ -1811,11 +1811,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Distance from pollution source</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.0009874389498011774</v>
+        <v>0.001386163037744764</v>
       </c>
     </row>
     <row r="71">
@@ -1831,11 +1831,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.0007955224654830965</v>
+        <v>0.00125312229176669</v>
       </c>
     </row>
     <row r="72">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.007225983161857244</v>
+        <v>0.009074970190729345</v>
       </c>
     </row>
     <row r="73">
@@ -1871,11 +1871,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.005403929475467067</v>
+        <v>0.00613936054490523</v>
       </c>
     </row>
     <row r="74">
@@ -1891,11 +1891,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.003330837102180339</v>
+        <v>0.005600820712900258</v>
       </c>
     </row>
     <row r="75">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.003209771005819562</v>
+        <v>0.005000729215604452</v>
       </c>
     </row>
     <row r="76">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>clay content</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.002870298842902912</v>
+        <v>0.004113146400670758</v>
       </c>
     </row>
     <row r="77">
@@ -1951,11 +1951,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>clay content</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.002295043379915569</v>
+        <v>0.003735522304739334</v>
       </c>
     </row>
     <row r="78">
@@ -1971,11 +1971,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.002267333869939989</v>
+        <v>0.003382017353793571</v>
       </c>
     </row>
     <row r="79">
@@ -1991,11 +1991,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>water content</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.002246652162962164</v>
+        <v>0.003366689962460328</v>
       </c>
     </row>
     <row r="80">
@@ -2011,11 +2011,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>Particle content</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.001560067341747526</v>
+        <v>0.003117760634287378</v>
       </c>
     </row>
     <row r="81">
@@ -2031,11 +2031,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Particle content</t>
+          <t>sand content</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.001233538867655284</v>
+        <v>0.00294127012539434</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/shap_rank_compare.xlsx
+++ b/outputs/shap_rank_compare.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>mean_abs_shap</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>model_select_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -446,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -455,7 +460,12 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.002985350077146904</v>
+        <v>0.004181256971495353</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -466,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -475,7 +485,12 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.001895417864811435</v>
+        <v>0.004011040934275321</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -486,16 +501,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.00163546158123836</v>
+        <v>0.003156569263638484</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -506,16 +526,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.001593826710928852</v>
+        <v>0.002516838120212849</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -526,16 +551,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Particle content</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.001518609059984328</v>
+        <v>0.002365795136496809</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -546,16 +576,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.001352892925951892</v>
+        <v>0.002322729076617898</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -566,16 +601,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>water content</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.001343562242622056</v>
+        <v>0.002251226162320279</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -586,16 +626,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>soil type</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.001298728128061271</v>
+        <v>0.002180632850325224</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -606,16 +651,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>clay content</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.0009926296738822771</v>
+        <v>0.002057607285590754</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -626,16 +676,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>clay content</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.0009301586022462516</v>
+        <v>0.001960569555601543</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -646,7 +701,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -655,7 +710,12 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.008442509671309393</v>
+        <v>0.01945627106205602</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -666,7 +726,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -675,7 +735,12 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.0053632803351059</v>
+        <v>0.01104523994996153</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -686,16 +751,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.002072383727660449</v>
+        <v>0.009385957811048439</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -706,16 +776,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.002069257706163208</v>
+        <v>0.006132196388766067</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -726,16 +801,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.001658777789270421</v>
+        <v>0.006025093318058323</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -746,16 +826,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vegetation cover type</t>
+          <t>Particle content</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.001486720971068863</v>
+        <v>0.004534913160928856</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -766,7 +851,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -775,7 +860,12 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.001396008814806924</v>
+        <v>0.004310098974291014</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -786,7 +876,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -795,7 +885,12 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.001353391208800569</v>
+        <v>0.004157524880436918</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -806,16 +901,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>clay content</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.001306386295864918</v>
+        <v>0.003918160215189692</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -826,7 +926,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -835,7 +935,12 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.001247905168373032</v>
+        <v>0.003658981196682457</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -846,7 +951,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -855,7 +960,12 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.001422442923228084</v>
+        <v>0.002626659673370852</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -866,16 +976,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Distance from pollution source</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.001363546420732245</v>
+        <v>0.002502687138109509</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -886,7 +1001,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -895,7 +1010,12 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.0008853263062860931</v>
+        <v>0.002009458740188741</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -906,16 +1026,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.0008764458329094064</v>
+        <v>0.001857027979709833</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -926,16 +1051,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>altitude</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.0008251862342868509</v>
+        <v>0.00184821471808495</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -946,16 +1076,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.0006355543323763054</v>
+        <v>0.00168453772832903</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -966,16 +1101,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>Distance from pollution source</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.0006265045699482417</v>
+        <v>0.001573950602236576</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -986,16 +1126,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.0006153696826327451</v>
+        <v>0.001479541997381418</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1006,7 +1151,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1015,7 +1160,12 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.0005921878909063309</v>
+        <v>0.001436646658535816</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1026,16 +1176,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.0005850770210008313</v>
+        <v>0.001386732364790842</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1046,7 +1201,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1055,7 +1210,12 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.002570680637866047</v>
+        <v>0.002898808091656324</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1066,16 +1226,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>altitude</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.002482781878158846</v>
+        <v>0.002633043225350748</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1086,16 +1251,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.001773142388002498</v>
+        <v>0.002505307524747465</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1106,16 +1276,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.001672626322820747</v>
+        <v>0.002412930739060099</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1126,16 +1301,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Particle content</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.001619668755754447</v>
+        <v>0.001691572939827144</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1146,16 +1326,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>clay content</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.001570283741417597</v>
+        <v>0.001668137505057681</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1166,16 +1351,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sand content</t>
+          <t>bulk density</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.001490883894564874</v>
+        <v>0.001460191362573618</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1186,16 +1376,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.001416304155015524</v>
+        <v>0.001425930131833066</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1206,16 +1401,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.001366394763293215</v>
+        <v>0.001378933131329811</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1226,16 +1426,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>sand content</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.001365630607525929</v>
+        <v>0.001365135802140689</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1246,7 +1451,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1255,7 +1460,12 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.008148636287739276</v>
+        <v>0.01180051248062248</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1266,16 +1476,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.004619357069258469</v>
+        <v>0.006048758472787132</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1286,16 +1501,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.003170523645533209</v>
+        <v>0.004492975564503009</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1306,16 +1526,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.002615323747435834</v>
+        <v>0.004341368259280918</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1326,16 +1551,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>bulk density</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.002565466241682067</v>
+        <v>0.004269311585828695</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1346,16 +1576,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sand content</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.002092652056340221</v>
+        <v>0.003417955869380259</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1366,16 +1601,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>sand content</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.002053936337194521</v>
+        <v>0.003087053188142438</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1386,16 +1626,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>clay content</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.001568497467498666</v>
+        <v>0.00299998473734655</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1406,16 +1651,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.001519174851465614</v>
+        <v>0.002882789233405329</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1426,16 +1676,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.001368722017900121</v>
+        <v>0.00258220035787186</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1446,7 +1701,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1455,7 +1710,12 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.01673277497997837</v>
+        <v>0.04064959405892918</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -1466,7 +1726,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1475,7 +1735,12 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.007356563851002161</v>
+        <v>0.01393795279513638</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1486,16 +1751,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.00578472159485509</v>
+        <v>0.01317807301656327</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1506,16 +1776,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.003695715855752893</v>
+        <v>0.01139984753853379</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1526,16 +1801,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>bulk density</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.002613491878010151</v>
+        <v>0.01096053885043365</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1546,16 +1826,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.002608478485367729</v>
+        <v>0.009935510443323336</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -1566,16 +1851,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.001865640612876551</v>
+        <v>0.00963246138647458</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1586,16 +1876,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>bulk density</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.001801180611410288</v>
+        <v>0.009439578342554144</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -1606,16 +1901,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sand content</t>
+          <t>Land use type</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.0008445157547234119</v>
+        <v>0.008049995057287266</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -1626,16 +1926,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>soil type</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.0008385338230732261</v>
+        <v>0.006915921181104416</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -1646,16 +1951,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>Distance from pollution source</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.002485803789015704</v>
+        <v>0.004046459468343555</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -1666,16 +1976,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.002389821749395334</v>
+        <v>0.0038617981929511</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1686,16 +2001,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Particle content</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.002360550699280148</v>
+        <v>0.003843579320068783</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -1706,7 +2026,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1715,7 +2035,12 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.002251560983886866</v>
+        <v>0.003405455466254168</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -1726,7 +2051,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1735,7 +2060,12 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.002243968037344277</v>
+        <v>0.002973890557640164</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -1746,16 +2076,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>bulk density</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.002239872375472674</v>
+        <v>0.002659779931757458</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -1766,16 +2101,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>bulk density</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.001974183636384278</v>
+        <v>0.002510470875195883</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -1786,16 +2126,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sand content</t>
+          <t>water content</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.001688511038669794</v>
+        <v>0.002378986473800059</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -1806,16 +2151,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>altitude</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.001386163037744764</v>
+        <v>0.002177881487148202</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -1826,16 +2176,21 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Particle content</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.00125312229176669</v>
+        <v>0.002141918966009501</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -1846,7 +2201,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1855,7 +2210,12 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.009074970190729345</v>
+        <v>0.01311496714569219</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -1866,16 +2226,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.00613936054490523</v>
+        <v>0.005681412954333808</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -1886,16 +2251,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.005600820712900258</v>
+        <v>0.005504433387972558</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -1906,7 +2276,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1915,7 +2285,12 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.005000729215604452</v>
+        <v>0.005132709768756866</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -1926,16 +2301,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>clay content</t>
+          <t>Particle content</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.004113146400670758</v>
+        <v>0.004727753997604341</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -1946,16 +2326,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.003735522304739334</v>
+        <v>0.003883385137788955</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -1966,16 +2351,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.003382017353793571</v>
+        <v>0.003554722286428528</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -1986,16 +2376,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>sand content</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.003366689962460328</v>
+        <v>0.00327551067453169</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -2006,16 +2401,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Particle content</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.003117760634287378</v>
+        <v>0.003233995005182193</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -2026,16 +2426,21 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>catboost</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>sand content</t>
+          <t>clay content</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.00294127012539434</v>
+        <v>0.003189002976610604</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>holdout_70_30/metrics_holdout.xlsx</t>
+        </is>
       </c>
     </row>
   </sheetData>
